--- a/dataset/DevelopmentBenchmark/Task06/tc06_output01.xlsx
+++ b/dataset/DevelopmentBenchmark/Task06/tc06_output01.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Fare</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Cabin</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Embarked</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Pclass</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SibSp</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Parch</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>HasCabin</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Embarked_C</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Embarked_Q</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Embarked_S</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5433513806577553</v>
+        <v>0.543</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.07722109457217767</v>
+        <v>-0.077</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2573065223849624</v>
+        <v>0.257</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3169115231122962</v>
+        <v>-0.338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1086686710178741</v>
+        <v>-0.035</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.156</v>
       </c>
     </row>
   </sheetData>
